--- a/Assets/GameResource/Excel/词条表.xlsx
+++ b/Assets/GameResource/Excel/词条表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Demo\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{520B12F0-4429-45E8-AD8F-A4D0C56EE583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A61AC9-04CE-4614-A4C7-BE97E6544271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -75,10 +75,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>攻击最虚弱的目标，杀死目标吸血效果翻倍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>下回合恢复等量生命</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -95,6 +91,26 @@
   </si>
   <si>
     <t>目标本回合受伤次数越多，伤害越高（基础伤害+连击修正n*受伤次数）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只能攻击最虚弱的目标，杀死目标吸血效果翻倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>迟缓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>该敌人在自己回合开始后跳过行动然后取消迟缓，不可叠加</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盗窃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有概率盗取目标身上的物资或金币，成功盗窃的目标不能再选择</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -420,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="63.88671875" customWidth="1"/>
@@ -478,7 +494,7 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -486,10 +502,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
         <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -500,7 +516,7 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -508,10 +524,32 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
         <v>16</v>
       </c>
-      <c r="C8" t="s">
-        <v>17</v>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/GameResource/Excel/词条表.xlsx
+++ b/Assets/GameResource/Excel/词条表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Demo\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A61AC9-04CE-4614-A4C7-BE97E6544271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD1F0C2-3942-4945-A154-FB9DEB648112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,9 +83,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>敌人回合受到伤害有概率立刻闪避并触发一次免费使用</t>
-  </si>
-  <si>
     <t>连击</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -111,6 +108,10 @@
   </si>
   <si>
     <t>有概率盗取目标身上的物资或金币，成功盗窃的目标不能再选择</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌人回合受到伤害有概率立刻闪避并触发一次效果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -505,7 +506,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -516,7 +517,7 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -524,10 +525,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
         <v>15</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -535,10 +536,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
         <v>18</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -546,10 +547,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
         <v>20</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
